--- a/hall/resources/sample/SeasonGemCraft.xlsx
+++ b/hall/resources/sample/SeasonGemCraft.xlsx
@@ -136,16 +136,16 @@
     <t>FailKeepAmount</t>
   </si>
   <si>
-    <t>10102_100_1|10202_100_1|20102_100_1|20202_100_1|30102_100_1|30202_100_1</t>
+    <t>100102_100_1|100107_100_1|100202_100_1|100207_100_1|100302_100_1|100307_100_1</t>
   </si>
   <si>
-    <t>10103_100_1|10203_100_1|20103_100_1|20203_100_1|30103_100_1|30203_100_1</t>
+    <t>100103_100_1|100108_100_1|100203_100_1|100208_100_1|100303_100_1|100308_100_1</t>
   </si>
   <si>
-    <t>10104_100_1|10204_100_1|20104_100_1|20204_100_1|30104_100_1|30204_100_1</t>
+    <t>100104_100_1|100109_100_1|100204_100_1|100209_100_1|100304_100_1|100309_100_1</t>
   </si>
   <si>
-    <t>10105_100_1|10205_100_1|20105_100_1|20205_100_1|30105_100_1|30205_100_1</t>
+    <t>100105_100_1|100110_100_1|100205_100_1|100210_100_1|100305_100_1|100310_100_1</t>
   </si>
 </sst>
 </file>
@@ -1525,6 +1525,9 @@
       <c r="A11">
         <v>10101</v>
       </c>
+      <c r="B11">
+        <v>100101</v>
+      </c>
       <c r="P11" t="str">
         <f t="shared" ref="P11:U11" si="0">_xlfn.TEXTJOIN("|",TRUE,P12:P17)</f>
         <v>10102_100_1|10202_100_1|20102_100_1|20202_100_1|30102_100_1|30202_100_1</v>
@@ -1546,6 +1549,9 @@
       <c r="A12">
         <v>10102</v>
       </c>
+      <c r="B12">
+        <v>100102</v>
+      </c>
       <c r="F12">
         <v>100</v>
       </c>
@@ -1565,11 +1571,11 @@
         <v>10105</v>
       </c>
       <c r="P12" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,I12,F12,G12)</f>
+        <f t="shared" ref="P12:P17" si="1">_xlfn.TEXTJOIN("_",TRUE,I12,F12,G12)</f>
         <v>10102_100_1</v>
       </c>
       <c r="R12" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,J12,$F$12,$G$12)</f>
+        <f t="shared" ref="R12:R17" si="2">_xlfn.TEXTJOIN("_",TRUE,J12,$F$12,$G$12)</f>
         <v>10103_100_1</v>
       </c>
       <c r="T12" t="str">
@@ -1577,7 +1583,7 @@
         <v>10104_100_1</v>
       </c>
       <c r="U12" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L12,$F$12,$G$12)</f>
+        <f t="shared" ref="U12:U17" si="3">_xlfn.TEXTJOIN("_",TRUE,L12,$F$12,$G$12)</f>
         <v>10105_100_1</v>
       </c>
     </row>
@@ -1585,6 +1591,9 @@
       <c r="A13">
         <v>10103</v>
       </c>
+      <c r="B13">
+        <v>100103</v>
+      </c>
       <c r="F13">
         <v>100</v>
       </c>
@@ -1604,19 +1613,19 @@
         <v>10205</v>
       </c>
       <c r="P13" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,I13,F13,G13)</f>
+        <f t="shared" si="1"/>
         <v>10202_100_1</v>
       </c>
       <c r="R13" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,J13,$F$12,$G$12)</f>
+        <f t="shared" si="2"/>
         <v>10203_100_1</v>
       </c>
       <c r="T13" t="str">
-        <f t="shared" ref="T13:T18" si="1">_xlfn.TEXTJOIN("_",TRUE,K13,$F$12,$G$12)</f>
+        <f t="shared" ref="T13:T18" si="4">_xlfn.TEXTJOIN("_",TRUE,K13,$F$12,$G$12)</f>
         <v>10204_100_1</v>
       </c>
       <c r="U13" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L13,$F$12,$G$12)</f>
+        <f t="shared" si="3"/>
         <v>10205_100_1</v>
       </c>
     </row>
@@ -1624,6 +1633,9 @@
       <c r="A14">
         <v>10104</v>
       </c>
+      <c r="B14">
+        <v>100104</v>
+      </c>
       <c r="F14">
         <v>100</v>
       </c>
@@ -1643,19 +1655,19 @@
         <v>20105</v>
       </c>
       <c r="P14" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,I14,F14,G14)</f>
+        <f t="shared" si="1"/>
         <v>20102_100_1</v>
       </c>
       <c r="R14" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,J14,$F$12,$G$12)</f>
+        <f t="shared" si="2"/>
         <v>20103_100_1</v>
       </c>
       <c r="T14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>20104_100_1</v>
       </c>
       <c r="U14" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L14,$F$12,$G$12)</f>
+        <f t="shared" si="3"/>
         <v>20105_100_1</v>
       </c>
     </row>
@@ -1663,6 +1675,9 @@
       <c r="A15">
         <v>10105</v>
       </c>
+      <c r="B15">
+        <v>100105</v>
+      </c>
       <c r="F15">
         <v>100</v>
       </c>
@@ -1682,19 +1697,19 @@
         <v>20205</v>
       </c>
       <c r="P15" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,I15,F15,G15)</f>
+        <f t="shared" si="1"/>
         <v>20202_100_1</v>
       </c>
       <c r="R15" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,J15,$F$12,$G$12)</f>
+        <f t="shared" si="2"/>
         <v>20203_100_1</v>
       </c>
       <c r="T15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>20204_100_1</v>
       </c>
       <c r="U15" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L15,$F$12,$G$12)</f>
+        <f t="shared" si="3"/>
         <v>20205_100_1</v>
       </c>
     </row>
@@ -1702,6 +1717,9 @@
       <c r="A16">
         <v>10201</v>
       </c>
+      <c r="B16">
+        <v>100106</v>
+      </c>
       <c r="F16">
         <v>100</v>
       </c>
@@ -1721,19 +1739,19 @@
         <v>30105</v>
       </c>
       <c r="P16" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,I16,F16,G16)</f>
+        <f t="shared" si="1"/>
         <v>30102_100_1</v>
       </c>
       <c r="R16" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,J16,$F$12,$G$12)</f>
+        <f t="shared" si="2"/>
         <v>30103_100_1</v>
       </c>
       <c r="T16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>30104_100_1</v>
       </c>
       <c r="U16" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L16,$F$12,$G$12)</f>
+        <f t="shared" si="3"/>
         <v>30105_100_1</v>
       </c>
     </row>
@@ -1741,6 +1759,9 @@
       <c r="A17">
         <v>10202</v>
       </c>
+      <c r="B17">
+        <v>100107</v>
+      </c>
       <c r="F17">
         <v>100</v>
       </c>
@@ -1760,19 +1781,19 @@
         <v>30205</v>
       </c>
       <c r="P17" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,I17,F17,G17)</f>
+        <f t="shared" si="1"/>
         <v>30202_100_1</v>
       </c>
       <c r="R17" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,J17,$F$12,$G$12)</f>
+        <f t="shared" si="2"/>
         <v>30203_100_1</v>
       </c>
       <c r="T17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>30204_100_1</v>
       </c>
       <c r="U17" t="str">
-        <f>_xlfn.TEXTJOIN("_",TRUE,L17,$F$12,$G$12)</f>
+        <f t="shared" si="3"/>
         <v>30205_100_1</v>
       </c>
     </row>
@@ -1780,115 +1801,374 @@
       <c r="A18">
         <v>10203</v>
       </c>
+      <c r="B18">
+        <v>100108</v>
+      </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19">
         <v>10204</v>
       </c>
+      <c r="B19">
+        <v>100109</v>
+      </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20">
         <v>10205</v>
       </c>
+      <c r="B20">
+        <v>100110</v>
+      </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21">
         <v>20101</v>
       </c>
+      <c r="B21">
+        <v>100201</v>
+      </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22">
         <v>20102</v>
       </c>
+      <c r="B22">
+        <v>100202</v>
+      </c>
+      <c r="P22" t="str">
+        <f t="shared" ref="P22:S22" si="5">_xlfn.TEXTJOIN("|",TRUE,P23:P28)</f>
+        <v>100102_100_1|100107_100_1|100202_100_1|100207_100_1|100302_100_1|100307_100_1</v>
+      </c>
+      <c r="Q22" t="str">
+        <f t="shared" si="5"/>
+        <v>100103_100_1|100108_100_1|100203_100_1|100208_100_1|100303_100_1|100308_100_1</v>
+      </c>
+      <c r="R22" t="str">
+        <f t="shared" si="5"/>
+        <v>100104_100_1|100109_100_1|100204_100_1|100209_100_1|100304_100_1|100309_100_1</v>
+      </c>
+      <c r="S22" t="str">
+        <f t="shared" si="5"/>
+        <v>100105_100_1|100110_100_1|100205_100_1|100210_100_1|100305_100_1|100310_100_1</v>
+      </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
         <v>20103</v>
       </c>
+      <c r="B23">
+        <v>100203</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>100102</v>
+      </c>
+      <c r="J23">
+        <v>100103</v>
+      </c>
+      <c r="K23">
+        <v>100104</v>
+      </c>
+      <c r="L23">
+        <v>100105</v>
+      </c>
+      <c r="P23" t="str">
+        <f t="shared" ref="P23:S23" si="6">_xlfn.TEXTJOIN("_",TRUE,I23,$F$23,$G$23)</f>
+        <v>100102_100_1</v>
+      </c>
+      <c r="Q23" t="str">
+        <f t="shared" si="6"/>
+        <v>100103_100_1</v>
+      </c>
+      <c r="R23" t="str">
+        <f t="shared" si="6"/>
+        <v>100104_100_1</v>
+      </c>
+      <c r="S23" t="str">
+        <f t="shared" si="6"/>
+        <v>100105_100_1</v>
+      </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
         <v>20104</v>
       </c>
+      <c r="B24">
+        <v>100204</v>
+      </c>
+      <c r="I24">
+        <v>100107</v>
+      </c>
+      <c r="J24">
+        <v>100108</v>
+      </c>
+      <c r="K24">
+        <v>100109</v>
+      </c>
+      <c r="L24">
+        <v>100110</v>
+      </c>
+      <c r="P24" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,I24,$F$23,$G$23)</f>
+        <v>100107_100_1</v>
+      </c>
+      <c r="Q24" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,J24,$F$23,$G$23)</f>
+        <v>100108_100_1</v>
+      </c>
+      <c r="R24" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,K24,$F$23,$G$23)</f>
+        <v>100109_100_1</v>
+      </c>
+      <c r="S24" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L24,$F$23,$G$23)</f>
+        <v>100110_100_1</v>
+      </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
         <v>20105</v>
       </c>
+      <c r="B25">
+        <v>100205</v>
+      </c>
+      <c r="I25">
+        <v>100202</v>
+      </c>
+      <c r="J25">
+        <v>100203</v>
+      </c>
+      <c r="K25">
+        <v>100204</v>
+      </c>
+      <c r="L25">
+        <v>100205</v>
+      </c>
+      <c r="P25" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,I25,$F$23,$G$23)</f>
+        <v>100202_100_1</v>
+      </c>
+      <c r="Q25" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,J25,$F$23,$G$23)</f>
+        <v>100203_100_1</v>
+      </c>
+      <c r="R25" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,K25,$F$23,$G$23)</f>
+        <v>100204_100_1</v>
+      </c>
+      <c r="S25" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L25,$F$23,$G$23)</f>
+        <v>100205_100_1</v>
+      </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26">
         <v>20201</v>
       </c>
+      <c r="B26">
+        <v>100206</v>
+      </c>
+      <c r="I26">
+        <v>100207</v>
+      </c>
+      <c r="J26">
+        <v>100208</v>
+      </c>
+      <c r="K26">
+        <v>100209</v>
+      </c>
+      <c r="L26">
+        <v>100210</v>
+      </c>
+      <c r="P26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,I26,$F$23,$G$23)</f>
+        <v>100207_100_1</v>
+      </c>
+      <c r="Q26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,J26,$F$23,$G$23)</f>
+        <v>100208_100_1</v>
+      </c>
+      <c r="R26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,K26,$F$23,$G$23)</f>
+        <v>100209_100_1</v>
+      </c>
+      <c r="S26" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L26,$F$23,$G$23)</f>
+        <v>100210_100_1</v>
+      </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27">
         <v>20202</v>
       </c>
+      <c r="B27">
+        <v>100207</v>
+      </c>
+      <c r="I27">
+        <v>100302</v>
+      </c>
+      <c r="J27">
+        <v>100303</v>
+      </c>
+      <c r="K27">
+        <v>100304</v>
+      </c>
+      <c r="L27">
+        <v>100305</v>
+      </c>
+      <c r="P27" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,I27,$F$23,$G$23)</f>
+        <v>100302_100_1</v>
+      </c>
+      <c r="Q27" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,J27,$F$23,$G$23)</f>
+        <v>100303_100_1</v>
+      </c>
+      <c r="R27" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,K27,$F$23,$G$23)</f>
+        <v>100304_100_1</v>
+      </c>
+      <c r="S27" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L27,$F$23,$G$23)</f>
+        <v>100305_100_1</v>
+      </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28">
         <v>20203</v>
       </c>
+      <c r="B28">
+        <v>100208</v>
+      </c>
+      <c r="I28">
+        <v>100307</v>
+      </c>
+      <c r="J28">
+        <v>100308</v>
+      </c>
+      <c r="K28">
+        <v>100309</v>
+      </c>
+      <c r="L28">
+        <v>100310</v>
+      </c>
+      <c r="P28" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,I28,$F$23,$G$23)</f>
+        <v>100307_100_1</v>
+      </c>
+      <c r="Q28" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,J28,$F$23,$G$23)</f>
+        <v>100308_100_1</v>
+      </c>
+      <c r="R28" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,K28,$F$23,$G$23)</f>
+        <v>100309_100_1</v>
+      </c>
+      <c r="S28" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,L28,$F$23,$G$23)</f>
+        <v>100310_100_1</v>
+      </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29">
         <v>20204</v>
       </c>
+      <c r="B29">
+        <v>100209</v>
+      </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30">
         <v>20205</v>
       </c>
+      <c r="B30">
+        <v>100210</v>
+      </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31">
         <v>30101</v>
       </c>
+      <c r="B31">
+        <v>100301</v>
+      </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32">
         <v>30102</v>
       </c>
-    </row>
-    <row r="33" spans="1:1">
+      <c r="B32">
+        <v>100302</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
       <c r="A33">
         <v>30103</v>
       </c>
-    </row>
-    <row r="34" spans="1:1">
+      <c r="B33">
+        <v>100303</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
       <c r="A34">
         <v>30104</v>
       </c>
-    </row>
-    <row r="35" spans="1:1">
+      <c r="B34">
+        <v>100304</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
       <c r="A35">
         <v>30105</v>
       </c>
-    </row>
-    <row r="36" spans="1:1">
+      <c r="B35">
+        <v>100305</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
       <c r="A36">
         <v>30201</v>
       </c>
-    </row>
-    <row r="37" spans="1:1">
+      <c r="B36">
+        <v>100306</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
       <c r="A37">
         <v>30202</v>
       </c>
-    </row>
-    <row r="38" spans="1:1">
+      <c r="B37">
+        <v>100307</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
       <c r="A38">
         <v>30203</v>
       </c>
-    </row>
-    <row r="39" spans="1:1">
+      <c r="B38">
+        <v>100308</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
       <c r="A39">
         <v>30204</v>
       </c>
-    </row>
-    <row r="40" spans="1:1">
+      <c r="B39">
+        <v>100309</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
       <c r="A40">
         <v>30205</v>
+      </c>
+      <c r="B40">
+        <v>100310</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/SeasonGemCraft.xlsx
+++ b/hall/resources/sample/SeasonGemCraft.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
@@ -311,12 +316,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1401,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>16</v>
@@ -1424,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>17</v>
@@ -1447,7 +1452,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>18</v>
@@ -1470,7 +1475,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>19</v>
@@ -1493,7 +1498,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>19</v>
